--- a/Matlab/Result.xlsx
+++ b/Matlab/Result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University\Control\LAB\FRA233_Lab3_State_Estimation\Matlab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E9DB8A-B474-45DC-83B3-01095C24B30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE073260-97B6-4F49-ADA7-11FFBDF00113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00F4D849-F711-48DE-A4AF-4E10A7678344}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Spring Constant (K)</t>
   </si>
@@ -48,6 +48,21 @@
   </si>
   <si>
     <t>3 Nut</t>
+  </si>
+  <si>
+    <t>4 Nut</t>
+  </si>
+  <si>
+    <t>2 Nut</t>
+  </si>
+  <si>
+    <t>1 Nut</t>
+  </si>
+  <si>
+    <t>K avg</t>
+  </si>
+  <si>
+    <t>C avg</t>
   </si>
 </sst>
 </file>
@@ -117,10 +132,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -457,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA157924-EA65-4EDF-A9F1-0F631F37B61B}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="25.77734375" defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.77734375" style="1"/>
@@ -465,7 +480,7 @@
     <col min="3" max="16384" width="25.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -474,64 +489,132 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:5" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4">
-        <v>34.921327382823002</v>
+      <c r="B2" s="3">
+        <v>27.153203325530299</v>
       </c>
       <c r="C2" s="2">
-        <v>0.107950669577367</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="2">
-        <v>28.138523869201698</v>
-      </c>
-      <c r="C3" s="2">
-        <v>8.3941996029546995E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
+        <v>7.2209624079431003E-2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1">
+        <f>AVERAGE(B2:B14)</f>
+        <v>27.289712211647718</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1">
+        <f>AVERAGE(C2:C14)</f>
+        <v>0.10913924279431719</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>27.272987052852901</v>
+      </c>
+      <c r="C5" s="2">
+        <v>6.1237299694885998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
-        <v>26.096968390053501</v>
-      </c>
-      <c r="C5" s="2">
-        <v>4.1773010672273E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2">
-        <v>28.533415406419401</v>
-      </c>
-      <c r="C6" s="2">
-        <v>8.8594804179063999E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="2">
-        <v>26.982144058443598</v>
-      </c>
-      <c r="C7" s="2">
-        <v>4.0264570529273E-2</v>
-      </c>
+      <c r="B8" s="2">
+        <v>27.960826749652199</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.107594306709629</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2">
+        <v>26.2740226904588</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.180219928231591</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2">
+        <v>27.7875212397444</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.124435055256049</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
